--- a/appointment_forms/047_insurance_policy_review_appointment_form_template--appointment_forms.xlsx
+++ b/appointment_forms/047_insurance_policy_review_appointment_form_template--appointment_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,10 +515,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>policy_number</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Policy Number</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the policy number</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -533,15 +537,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>policy_date</t>
+          <t>policy_start_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Policy Start Date</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter start date</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -551,20 +559,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>policy_time</t>
+          <t>policy_end_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Policy End Date</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter end date</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>policy_agent</t>
+          <t>agent_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter agent's name</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,10 +623,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>client_name</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Client Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter client's name</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,10 +650,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Client Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter client's email</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,10 +677,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Client Phone</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter client's phone number</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,18 +699,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>appointment_start_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter start date of the appointment</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,39 +726,101 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>appointment_end_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter end date of the appointment</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>appointment_time</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter start time</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>appointment_duration</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter appointment duration</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>appointment_note</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter any additional notes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
